--- a/apps/home/homepage/fixtures/roinsight.xlsx
+++ b/apps/home/homepage/fixtures/roinsight.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Backup\ng\backend\api\apps\home\homepage\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammad.hamoud\Desktop\ng\backend\project\apps\home\homepage\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CA4F3D-D2C8-490E-B6CC-9A40176F459E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121F2AB0-4DBE-4C6C-B3ED-9DC719BB3FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="480" windowWidth="29040" windowHeight="15840" tabRatio="660" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="660" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,10 @@
     <sheet name="offering" sheetId="5" r:id="rId10"/>
     <sheet name="testimonial" sheetId="9" r:id="rId11"/>
     <sheet name="all" sheetId="13" r:id="rId12"/>
+    <sheet name="pricing_section" sheetId="15" r:id="rId13"/>
+    <sheet name="pricing_plan" sheetId="16" r:id="rId14"/>
+    <sheet name="pricing_feature" sheetId="17" r:id="rId15"/>
+    <sheet name="pricing_plan_limit" sheetId="18" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="468">
   <si>
     <t>name</t>
   </si>
@@ -911,6 +915,546 @@
   </si>
   <si>
     <t>نحن نقدم نظرة شاملة على الأدوات الشهيرة في علم البيانات والذكاء التجاري. من تصور البيانات إلى التحليلات المتقدمة وتعلم الآلة، يغطي كل ما يلزم لاتخاذ قرارات مستنيرة حول اختيار الأدوات. بايثون هي لغة مترجمة مستوى عالٍ، بينما يستخدم R في الحوسبة الإحصائية والرسومات. تقدم Tableau تصور البيانات والتحليلات، بينما يعد PowerBI خدمة تحليلات الأعمال التي تقدمها مايكروسوفت، ويُعتبر Excel برنامج جداول بيانات معروف عالميًا.</t>
+  </si>
+  <si>
+    <t>Pricing Plans</t>
+  </si>
+  <si>
+    <t>Choose the plan that fits your business intelligence needs.</t>
+  </si>
+  <si>
+    <t>خطط الأسعار</t>
+  </si>
+  <si>
+    <t>اختر الخطة التي تناسب احتياجات ذكاء الأعمال الخاصة بك.</t>
+  </si>
+  <si>
+    <t>pricing_plans</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>short_description</t>
+  </si>
+  <si>
+    <t>badge_text</t>
+  </si>
+  <si>
+    <t>price_label</t>
+  </si>
+  <si>
+    <t>button_text</t>
+  </si>
+  <si>
+    <t>button_url</t>
+  </si>
+  <si>
+    <t>billing_interval</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>compare_at_price</t>
+  </si>
+  <si>
+    <t>trial_days</t>
+  </si>
+  <si>
+    <t>setup_fee</t>
+  </si>
+  <si>
+    <t>is_free</t>
+  </si>
+  <si>
+    <t>is_custom_price</t>
+  </si>
+  <si>
+    <t>allow_subscribe</t>
+  </si>
+  <si>
+    <t>allow_contact_sales</t>
+  </si>
+  <si>
+    <t>sort_order</t>
+  </si>
+  <si>
+    <t>short_description_ar</t>
+  </si>
+  <si>
+    <t>badge_text_ar</t>
+  </si>
+  <si>
+    <t>price_label_ar</t>
+  </si>
+  <si>
+    <t>button_text_ar</t>
+  </si>
+  <si>
+    <t>button_url_ar</t>
+  </si>
+  <si>
+    <t>Starter</t>
+  </si>
+  <si>
+    <t>Essential BI for single properties.</t>
+  </si>
+  <si>
+    <t>Best for one hotel</t>
+  </si>
+  <si>
+    <t>Per Month</t>
+  </si>
+  <si>
+    <t>Get Started</t>
+  </si>
+  <si>
+    <t>/contact/</t>
+  </si>
+  <si>
+    <t>monthly</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>المبتدئة</t>
+  </si>
+  <si>
+    <t>ذكاء أعمال أساسي لفندق واحد.</t>
+  </si>
+  <si>
+    <t>الأفضل لفندق واحد</t>
+  </si>
+  <si>
+    <t>شهريًا</t>
+  </si>
+  <si>
+    <t>ابدأ الآن</t>
+  </si>
+  <si>
+    <t>starter</t>
+  </si>
+  <si>
+    <t>Professional</t>
+  </si>
+  <si>
+    <t>Advanced analytics for growing properties.</t>
+  </si>
+  <si>
+    <t>Most popular for growing teams</t>
+  </si>
+  <si>
+    <t>Most Popular</t>
+  </si>
+  <si>
+    <t>الاحترافية</t>
+  </si>
+  <si>
+    <t>تحليلات متقدمة للفنادق المتنامية.</t>
+  </si>
+  <si>
+    <t>الأكثر شيوعًا للفرق المتنامية</t>
+  </si>
+  <si>
+    <t>الأكثر شيوعًا</t>
+  </si>
+  <si>
+    <t>professional</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Powerful reporting for multi-property operations.</t>
+  </si>
+  <si>
+    <t>Best for hotel groups</t>
+  </si>
+  <si>
+    <t>Best Value</t>
+  </si>
+  <si>
+    <t>Choose Business</t>
+  </si>
+  <si>
+    <t>الأعمال</t>
+  </si>
+  <si>
+    <t>تقارير قوية للعمليات متعددة الفنادق.</t>
+  </si>
+  <si>
+    <t>الأفضل للمجموعات الفندقية</t>
+  </si>
+  <si>
+    <t>أفضل قيمة</t>
+  </si>
+  <si>
+    <t>اختر الأعمال</t>
+  </si>
+  <si>
+    <t>business</t>
+  </si>
+  <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
+    <t>Custom solution for chains and ownership groups.</t>
+  </si>
+  <si>
+    <t>Tailored enterprise offering</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>Contact Us</t>
+  </si>
+  <si>
+    <t>Talk To Sales</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>المؤسسات</t>
+  </si>
+  <si>
+    <t>حل مخصص للسلاسل والمجموعات المالكة.</t>
+  </si>
+  <si>
+    <t>عرض مخصص للمؤسسات</t>
+  </si>
+  <si>
+    <t>مخصص</t>
+  </si>
+  <si>
+    <t>تواصل معنا</t>
+  </si>
+  <si>
+    <t>تحدث إلى المبيعات</t>
+  </si>
+  <si>
+    <t>enterprise</t>
+  </si>
+  <si>
+    <t>plan</t>
+  </si>
+  <si>
+    <t>value_type</t>
+  </si>
+  <si>
+    <t>value_boolean</t>
+  </si>
+  <si>
+    <t>value_number</t>
+  </si>
+  <si>
+    <t>value_text_ar</t>
+  </si>
+  <si>
+    <t>Daily Revenue Dashboard</t>
+  </si>
+  <si>
+    <t>Track revenue performance daily</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>لوحة الإيرادات اليومية</t>
+  </si>
+  <si>
+    <t>تتبع أداء الإيرادات يوميًا.</t>
+  </si>
+  <si>
+    <t>starter_dashboard</t>
+  </si>
+  <si>
+    <t>Pickup Report</t>
+  </si>
+  <si>
+    <t>Monitor pickup changes daily</t>
+  </si>
+  <si>
+    <t>تقرير الحجوزات</t>
+  </si>
+  <si>
+    <t>راقب تغيرات الحجوزات يوميًا.</t>
+  </si>
+  <si>
+    <t>starter_pickup</t>
+  </si>
+  <si>
+    <t>Email Support</t>
+  </si>
+  <si>
+    <t>Basic email support</t>
+  </si>
+  <si>
+    <t>الدعم عبر البريد الإلكتروني</t>
+  </si>
+  <si>
+    <t>دعم أساسي عبر البريد الإلكتروني.</t>
+  </si>
+  <si>
+    <t>starter_email_support</t>
+  </si>
+  <si>
+    <t>Forecast Dashboard</t>
+  </si>
+  <si>
+    <t>View forecast trends</t>
+  </si>
+  <si>
+    <t>لوحة التوقعات</t>
+  </si>
+  <si>
+    <t>عرض اتجاهات التوقعات.</t>
+  </si>
+  <si>
+    <t>pro_forecast</t>
+  </si>
+  <si>
+    <t>Pace Analysis</t>
+  </si>
+  <si>
+    <t>Compare pace with previous periods</t>
+  </si>
+  <si>
+    <t>تحليل الوتيرة</t>
+  </si>
+  <si>
+    <t>قارن الوتيرة بالفترات السابقة.</t>
+  </si>
+  <si>
+    <t>pro_pace</t>
+  </si>
+  <si>
+    <t>Budget Comparison</t>
+  </si>
+  <si>
+    <t>Compare budget and actuals</t>
+  </si>
+  <si>
+    <t>مقارنة الميزانية</t>
+  </si>
+  <si>
+    <t>قارن الميزانية بالأداء الفعلي.</t>
+  </si>
+  <si>
+    <t>pro_budget</t>
+  </si>
+  <si>
+    <t>Multi Property Dashboard</t>
+  </si>
+  <si>
+    <t>Portfolio-wide insights</t>
+  </si>
+  <si>
+    <t>لوحة متعددة الفنادق</t>
+  </si>
+  <si>
+    <t>رؤى على مستوى جميع الفنادق.</t>
+  </si>
+  <si>
+    <t>business_multi_property</t>
+  </si>
+  <si>
+    <t>Automated Data Validation</t>
+  </si>
+  <si>
+    <t>Reduce reporting errors</t>
+  </si>
+  <si>
+    <t>التحقق الآلي من البيانات</t>
+  </si>
+  <si>
+    <t>تقليل أخطاء التقارير.</t>
+  </si>
+  <si>
+    <t>business_validation</t>
+  </si>
+  <si>
+    <t>Scheduled Executive Reports</t>
+  </si>
+  <si>
+    <t>Automatic leadership summaries</t>
+  </si>
+  <si>
+    <t>تقارير تنفيذية مجدولة</t>
+  </si>
+  <si>
+    <t>ملخصات تلقائية للإدارة.</t>
+  </si>
+  <si>
+    <t>business_reports</t>
+  </si>
+  <si>
+    <t>Custom Integration</t>
+  </si>
+  <si>
+    <t>Connect your systems</t>
+  </si>
+  <si>
+    <t>تكامل مخصص</t>
+  </si>
+  <si>
+    <t>اربط أنظمتك المختلفة.</t>
+  </si>
+  <si>
+    <t>enterprise_integration</t>
+  </si>
+  <si>
+    <t>Dedicated Success Manager</t>
+  </si>
+  <si>
+    <t>Assigned account specialist</t>
+  </si>
+  <si>
+    <t>مدير نجاح مخصص</t>
+  </si>
+  <si>
+    <t>أخصائي حساب مخصص.</t>
+  </si>
+  <si>
+    <t>enterprise_manager</t>
+  </si>
+  <si>
+    <t>SLA Support</t>
+  </si>
+  <si>
+    <t>Enterprise support coverage</t>
+  </si>
+  <si>
+    <t>دعم باتفاقية مستوى الخدمة</t>
+  </si>
+  <si>
+    <t>دعم مؤسسي باتفاقية مستوى خدمة.</t>
+  </si>
+  <si>
+    <t>enterprise_sla</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>limit_type</t>
+  </si>
+  <si>
+    <t>value_integer</t>
+  </si>
+  <si>
+    <t>value_decimal</t>
+  </si>
+  <si>
+    <t>unit_ar</t>
+  </si>
+  <si>
+    <t>custom_value_ar</t>
+  </si>
+  <si>
+    <t>Properties</t>
+  </si>
+  <si>
+    <t>hotel</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>الفنادق</t>
+  </si>
+  <si>
+    <t>فندق</t>
+  </si>
+  <si>
+    <t>starter_properties</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>المستخدمون</t>
+  </si>
+  <si>
+    <t>مستخدم</t>
+  </si>
+  <si>
+    <t>starter_users</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>per month</t>
+  </si>
+  <si>
+    <t>التقارير</t>
+  </si>
+  <si>
+    <t>starter_reports</t>
+  </si>
+  <si>
+    <t>hotels</t>
+  </si>
+  <si>
+    <t>فنادق</t>
+  </si>
+  <si>
+    <t>pro_properties</t>
+  </si>
+  <si>
+    <t>users</t>
+  </si>
+  <si>
+    <t>مستخدمون</t>
+  </si>
+  <si>
+    <t>pro_users</t>
+  </si>
+  <si>
+    <t>pro_reports</t>
+  </si>
+  <si>
+    <t>business_properties</t>
+  </si>
+  <si>
+    <t>business_users</t>
+  </si>
+  <si>
+    <t>API Access</t>
+  </si>
+  <si>
+    <t>الوصول إلى API</t>
+  </si>
+  <si>
+    <t>مضمن</t>
+  </si>
+  <si>
+    <t>business_api</t>
+  </si>
+  <si>
+    <t>unlimited</t>
+  </si>
+  <si>
+    <t>غير محدود</t>
+  </si>
+  <si>
+    <t>enterprise_properties</t>
+  </si>
+  <si>
+    <t>enterprise_users</t>
+  </si>
+  <si>
+    <t>enterprise_reports</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1598,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1078,34 +1622,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1128,29 +1657,19 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1647,10 +2166,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE354C8F-D76E-4D6E-B370-894F46303512}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.85546875" style="4" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="4" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="4" bestFit="1" customWidth="1"/>
@@ -1659,66 +2178,63 @@
     <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-    </row>
-    <row r="2" spans="1:10" ht="114.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="114.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="17" t="s">
         <v>281</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>282</v>
       </c>
       <c r="F2" t="s">
         <v>241</v>
       </c>
-      <c r="G2" s="18" t="str">
+      <c r="G2" s="14" t="str">
         <f t="shared" ref="G2" si="0">SUBSTITUTE(TRIM(LOWER(A2)), " ", "_")</f>
         <v>roinsight.com</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:7" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="17" t="s">
         <v>278</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>284</v>
       </c>
       <c r="F3" t="s">
@@ -1728,22 +2244,19 @@
         <f>SUBSTITUTE(TRIM(LOWER(A3)), " ", "_")</f>
         <v>business_intelligence_tool</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="72" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="17" t="s">
         <v>279</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="17" t="s">
         <v>285</v>
       </c>
       <c r="F4" t="s">
@@ -1753,22 +2266,19 @@
         <f t="shared" ref="G4:G5" si="1">SUBSTITUTE(TRIM(LOWER(A4)), " ", "_")</f>
         <v>revenue_management_consultation</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-    </row>
-    <row r="5" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="17" t="s">
         <v>280</v>
       </c>
       <c r="C5"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="17" t="s">
         <v>283</v>
       </c>
       <c r="F5" t="s">
@@ -1778,79 +2288,60 @@
         <f t="shared" si="1"/>
         <v>revenue_optimization_solutions</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="24"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="17"/>
       <c r="F6"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="23"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="D7" s="16"/>
       <c r="F7"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="23"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="16"/>
       <c r="F8"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="23"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="16"/>
       <c r="F9"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="23"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="16"/>
       <c r="F10"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1858,7 +2349,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="3"/>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
@@ -1895,11 +2386,11 @@
       <c r="D27" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A11:A13">
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1985,72 +2476,1378 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="21" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="21" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="21" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D590FC74-2DC3-458D-BF96-22D4D111E36A}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB4C729-1572-4F95-987E-59325F71CF78}">
+  <dimension ref="A1:AB5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J1" t="s">
+        <v>300</v>
+      </c>
+      <c r="K1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>307</v>
+      </c>
+      <c r="R1" t="s">
+        <v>308</v>
+      </c>
+      <c r="S1" t="s">
+        <v>309</v>
+      </c>
+      <c r="T1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V1" t="s">
+        <v>6</v>
+      </c>
+      <c r="W1" t="s">
+        <v>310</v>
+      </c>
+      <c r="X1" t="s">
+        <v>311</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K2">
+        <v>49</v>
+      </c>
+      <c r="L2">
+        <v>79</v>
+      </c>
+      <c r="M2">
+        <v>7</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>323</v>
+      </c>
+      <c r="V2" t="s">
+        <v>324</v>
+      </c>
+      <c r="W2" t="s">
+        <v>325</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>327</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K3">
+        <v>149</v>
+      </c>
+      <c r="L3">
+        <v>199</v>
+      </c>
+      <c r="M3">
+        <v>14</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="U3" t="s">
+        <v>333</v>
+      </c>
+      <c r="V3" t="s">
+        <v>334</v>
+      </c>
+      <c r="W3" t="s">
+        <v>335</v>
+      </c>
+      <c r="X3" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>327</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H4" t="s">
+        <v>320</v>
+      </c>
+      <c r="I4" t="s">
+        <v>321</v>
+      </c>
+      <c r="J4" t="s">
+        <v>322</v>
+      </c>
+      <c r="K4">
+        <v>299</v>
+      </c>
+      <c r="L4">
+        <v>399</v>
+      </c>
+      <c r="M4">
+        <v>14</v>
+      </c>
+      <c r="N4">
+        <v>49</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="U4" t="s">
+        <v>343</v>
+      </c>
+      <c r="V4" t="s">
+        <v>344</v>
+      </c>
+      <c r="W4" t="s">
+        <v>345</v>
+      </c>
+      <c r="X4" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I5" t="s">
+        <v>355</v>
+      </c>
+      <c r="J5" t="s">
+        <v>322</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>4</v>
+      </c>
+      <c r="T5" t="s">
+        <v>356</v>
+      </c>
+      <c r="U5" t="s">
+        <v>357</v>
+      </c>
+      <c r="V5" t="s">
+        <v>358</v>
+      </c>
+      <c r="W5" t="s">
+        <v>359</v>
+      </c>
+      <c r="X5" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B74D2FB-50D5-4305-9406-B1A306A24AA0}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>367</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J2" t="s">
+        <v>372</v>
+      </c>
+      <c r="L2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>376</v>
+      </c>
+      <c r="J3" t="s">
+        <v>377</v>
+      </c>
+      <c r="L3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D4" t="s">
+        <v>370</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>381</v>
+      </c>
+      <c r="J4" t="s">
+        <v>382</v>
+      </c>
+      <c r="L4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>386</v>
+      </c>
+      <c r="J5" t="s">
+        <v>387</v>
+      </c>
+      <c r="L5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" t="s">
+        <v>390</v>
+      </c>
+      <c r="D6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J6" t="s">
+        <v>392</v>
+      </c>
+      <c r="L6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>396</v>
+      </c>
+      <c r="J7" t="s">
+        <v>397</v>
+      </c>
+      <c r="L7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" t="s">
+        <v>370</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>401</v>
+      </c>
+      <c r="J8" t="s">
+        <v>402</v>
+      </c>
+      <c r="L8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" t="s">
+        <v>405</v>
+      </c>
+      <c r="D9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>406</v>
+      </c>
+      <c r="J9" t="s">
+        <v>407</v>
+      </c>
+      <c r="L9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D10" t="s">
+        <v>370</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>411</v>
+      </c>
+      <c r="J10" t="s">
+        <v>412</v>
+      </c>
+      <c r="L10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" t="s">
+        <v>415</v>
+      </c>
+      <c r="D11" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>416</v>
+      </c>
+      <c r="J11" t="s">
+        <v>417</v>
+      </c>
+      <c r="L11" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C12" t="s">
+        <v>420</v>
+      </c>
+      <c r="D12" t="s">
+        <v>370</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>421</v>
+      </c>
+      <c r="J12" t="s">
+        <v>422</v>
+      </c>
+      <c r="L12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13" t="s">
+        <v>370</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>426</v>
+      </c>
+      <c r="J13" t="s">
+        <v>427</v>
+      </c>
+      <c r="L13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B3B2EB4-F47A-46F0-99EA-081134C6F984}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>433</v>
+      </c>
+      <c r="K1" t="s">
+        <v>434</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>438</v>
+      </c>
+      <c r="J2" t="s">
+        <v>439</v>
+      </c>
+      <c r="L2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>443</v>
+      </c>
+      <c r="J3" t="s">
+        <v>444</v>
+      </c>
+      <c r="L3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>448</v>
+      </c>
+      <c r="J4" t="s">
+        <v>326</v>
+      </c>
+      <c r="L4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" t="s">
+        <v>437</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>438</v>
+      </c>
+      <c r="J5" t="s">
+        <v>451</v>
+      </c>
+      <c r="L5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" t="s">
+        <v>437</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J6" t="s">
+        <v>454</v>
+      </c>
+      <c r="L6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>448</v>
+      </c>
+      <c r="J7" t="s">
+        <v>326</v>
+      </c>
+      <c r="L7" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" t="s">
+        <v>437</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>438</v>
+      </c>
+      <c r="J8" t="s">
+        <v>451</v>
+      </c>
+      <c r="L8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>443</v>
+      </c>
+      <c r="J9" t="s">
+        <v>454</v>
+      </c>
+      <c r="L9" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B10" t="s">
+        <v>459</v>
+      </c>
+      <c r="D10" t="s">
+        <v>437</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>460</v>
+      </c>
+      <c r="K10" t="s">
+        <v>461</v>
+      </c>
+      <c r="L10" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C11" t="s">
+        <v>450</v>
+      </c>
+      <c r="D11" t="s">
+        <v>463</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>438</v>
+      </c>
+      <c r="J11" t="s">
+        <v>451</v>
+      </c>
+      <c r="K11" t="s">
+        <v>464</v>
+      </c>
+      <c r="L11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B12" t="s">
+        <v>441</v>
+      </c>
+      <c r="C12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" t="s">
+        <v>463</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>443</v>
+      </c>
+      <c r="J12" t="s">
+        <v>454</v>
+      </c>
+      <c r="K12" t="s">
+        <v>464</v>
+      </c>
+      <c r="L12" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" t="s">
+        <v>446</v>
+      </c>
+      <c r="C13" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" t="s">
+        <v>463</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>448</v>
+      </c>
+      <c r="J13" t="s">
+        <v>326</v>
+      </c>
+      <c r="K13" t="s">
+        <v>464</v>
+      </c>
+      <c r="L13" t="s">
+        <v>467</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2127,10 +3924,10 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>97143202204</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -2158,8 +3955,8 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -2187,113 +3984,112 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="7" width="23.85546875" style="9" customWidth="1"/>
+    <col min="1" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32"/>
-    </row>
-    <row r="3" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="22"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="22"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="15"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:C1">
@@ -2319,143 +4115,133 @@
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>241</v>
       </c>
-      <c r="B2"/>
       <c r="C2" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="14" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>242</v>
       </c>
-      <c r="B3"/>
       <c r="C3" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="14" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>243</v>
       </c>
-      <c r="B4"/>
       <c r="C4" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="14" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>244</v>
       </c>
-      <c r="B5"/>
       <c r="C5" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="14" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>245</v>
       </c>
-      <c r="B6"/>
       <c r="C6" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="14" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>246</v>
       </c>
-      <c r="B7"/>
       <c r="C7" t="s">
         <v>258</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="14" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>247</v>
       </c>
-      <c r="B8"/>
       <c r="C8" t="s">
         <v>259</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="14" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>248</v>
       </c>
-      <c r="B9"/>
       <c r="C9" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="14" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>249</v>
       </c>
-      <c r="B10"/>
       <c r="C10" t="s">
         <v>261</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="14" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>250</v>
       </c>
-      <c r="B11"/>
       <c r="C11" t="s">
         <v>262</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>275</v>
       </c>
     </row>
@@ -2466,7 +4252,7 @@
       <c r="C12" t="s">
         <v>263</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="14" t="s">
         <v>276</v>
       </c>
     </row>
@@ -2477,16 +4263,16 @@
       <c r="C13" t="s">
         <v>264</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="14" t="s">
         <v>269</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C1:F1">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2570,21 +4356,21 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J2" s="6"/>
-      <c r="K2" s="10"/>
+      <c r="K2" s="9"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="V2" s="39" t="s">
+      <c r="V2" s="26" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J3" s="6"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -2594,7 +4380,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J4" s="6"/>
-      <c r="K4" s="10"/>
+      <c r="K4" s="9"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -2633,7 +4419,7 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C13" s="13"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -2680,29 +4466,28 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="30.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.85546875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="77.28515625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="40.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="30.140625" style="9"/>
+    <col min="1" max="1" width="39.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.85546875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="77.28515625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="40.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -2710,241 +4495,241 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="21" t="s">
         <v>67</v>
       </c>
       <c r="C2"/>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="18" t="str">
+      <c r="F2" s="14" t="str">
         <f>SUBSTITUTE(TRIM(LOWER(A2)), " ", "_")</f>
         <v>system_integration_services</v>
       </c>
-      <c r="G2" s="33"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="21" t="s">
         <v>69</v>
       </c>
       <c r="C3"/>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="14" t="str">
         <f t="shared" ref="F3:F13" si="0">SUBSTITUTE(TRIM(LOWER(A3)), " ", "_")</f>
         <v>business_intelligence_tool</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="21" t="s">
         <v>71</v>
       </c>
       <c r="C4"/>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="18" t="str">
+      <c r="F4" s="14" t="str">
         <f t="shared" si="0"/>
         <v>advanced_automation_solutions</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C5"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="18" t="str">
+      <c r="F5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>performance_monitoring_systems</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C6"/>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="18" t="str">
+      <c r="F6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>tracking_solutions_systems</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C7"/>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="18" t="str">
+      <c r="F7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>data_portability_solutions</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="21" t="s">
         <v>79</v>
       </c>
       <c r="C8"/>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="18" t="str">
+      <c r="F8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>real-time_database_systems</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="21" t="s">
         <v>81</v>
       </c>
       <c r="C9"/>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="18" t="str">
+      <c r="F9" s="14" t="str">
         <f>SUBSTITUTE(TRIM(LOWER(A9)), " ", "_")</f>
         <v>digital_transformation_system</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="21" t="s">
         <v>83</v>
       </c>
       <c r="C10"/>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="18" t="str">
+      <c r="F10" s="14" t="str">
         <f t="shared" si="0"/>
         <v>transaction_processing_system</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="21" t="s">
         <v>85</v>
       </c>
       <c r="C11"/>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="18" t="str">
+      <c r="F11" s="14" t="str">
         <f t="shared" si="0"/>
         <v>management_information_system</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="21" t="s">
         <v>87</v>
       </c>
       <c r="C12"/>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="18" t="str">
+      <c r="F12" s="14" t="str">
         <f t="shared" si="0"/>
         <v>decision_support_system</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="21" t="s">
         <v>89</v>
       </c>
       <c r="C13"/>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="18" t="str">
+      <c r="F13" s="14" t="str">
         <f t="shared" si="0"/>
         <v>executive_support_system</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
       <c r="C14"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="18"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A15:A21">
@@ -2993,153 +4778,153 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="F2" s="18" t="str">
+      <c r="F2" s="14" t="str">
         <f t="shared" ref="F2:F9" si="0">SUBSTITUTE(TRIM(LOWER(A2)), " ", "_")</f>
         <v>unlock_the_power_of_your_data</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="14" t="str">
         <f t="shared" si="0"/>
         <v>stay_ahead_of_the_competition</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="23" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="F4" s="18" t="str">
+      <c r="F4" s="14" t="str">
         <f t="shared" si="0"/>
         <v>make_better_decisions,_faster</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="23" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F5" s="18" t="str">
+      <c r="F5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>simplify_your_workflow</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="23" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="18" t="str">
+      <c r="F6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>empower_your_team</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="23" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="F7" s="18" t="str">
+      <c r="F7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>see_the_big_picture</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="23" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="F8" s="18" t="str">
+      <c r="F8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>take_control_of_your_finances</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="23" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="F9" s="18" t="str">
+      <c r="F9" s="14" t="str">
         <f t="shared" si="0"/>
         <v>customizable_and_scalable</v>
       </c>
@@ -3187,361 +4972,361 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F2" s="18" t="str">
+      <c r="F2" s="14" t="str">
         <f t="shared" ref="F2:F21" si="0">SUBSTITUTE(TRIM(LOWER(A2)), " ", "_")</f>
         <v>customer_segmentation</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="14" t="str">
         <f t="shared" si="0"/>
         <v>predictive_analytics</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="18" t="str">
+      <c r="F4" s="14" t="str">
         <f t="shared" si="0"/>
         <v>sales_and_marketing_optimization</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="18" t="str">
+      <c r="F5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>demand_forecasting</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="F6" s="18" t="str">
+      <c r="F6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>pricing_optimization</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="18" t="str">
+      <c r="F7" s="14" t="str">
         <f>SUBSTITUTE(TRIM(LOWER(A7)), " ", "_")</f>
         <v>inventory_management</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F8" s="18" t="str">
+      <c r="F8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>revenue_analysis</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="18" t="str">
+      <c r="F9" s="14" t="str">
         <f t="shared" si="0"/>
         <v>competitive_analysis</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="18" t="str">
+      <c r="F10" s="14" t="str">
         <f t="shared" si="0"/>
         <v>channel_management</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="18" t="str">
+      <c r="F11" s="14" t="str">
         <f t="shared" si="0"/>
         <v>marketing_analytics</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="F12" s="18" t="str">
+      <c r="F12" s="14" t="str">
         <f t="shared" si="0"/>
         <v>customer_analytics</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="F13" s="18" t="str">
+      <c r="F13" s="14" t="str">
         <f t="shared" si="0"/>
         <v>forecast_accuracy_monitoring</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="18" t="str">
+      <c r="F14" s="14" t="str">
         <f t="shared" si="0"/>
         <v>roi_analysis</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F15" s="18" t="str">
+      <c r="F15" s="14" t="str">
         <f t="shared" si="0"/>
         <v>financial_modeling</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="F16" s="18" t="str">
+      <c r="F16" s="14" t="str">
         <f t="shared" si="0"/>
         <v>cost_optimization</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F17" s="18" t="str">
+      <c r="F17" s="14" t="str">
         <f t="shared" si="0"/>
         <v>risk_management</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="F18" s="18" t="str">
+      <c r="F18" s="14" t="str">
         <f t="shared" si="0"/>
         <v>performance_analysis</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="F19" s="18" t="str">
+      <c r="F19" s="14" t="str">
         <f t="shared" si="0"/>
         <v>investment_analysis</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="18" t="str">
+      <c r="F20" s="14" t="str">
         <f t="shared" si="0"/>
         <v>portfolio_optimization</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="F21" s="18" t="str">
+      <c r="F21" s="14" t="str">
         <f t="shared" si="0"/>
         <v>benchmarking</v>
       </c>
@@ -3560,7 +5345,7 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="35" customWidth="1"/>
+    <col min="1" max="1" width="30" style="28" customWidth="1"/>
     <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
@@ -3587,219 +5372,219 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18" t="str">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14" t="str">
         <f t="shared" ref="F2:F24" si="0">SUBSTITUTE(TRIM(LOWER(A2)), " ", "_")</f>
         <v>python</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18" t="str">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14" t="str">
         <f t="shared" si="0"/>
         <v>database</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18" t="str">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14" t="str">
         <f t="shared" si="0"/>
         <v>r</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18" t="str">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>tableau</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18" t="str">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>powerbi</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18" t="str">
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>excel</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="29"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="18" t="str">
+      <c r="A8" s="27"/>
+      <c r="B8" s="22"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="34"/>
-      <c r="B9" s="29"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="18" t="str">
+      <c r="A9" s="27"/>
+      <c r="B9" s="22"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="29"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="18" t="str">
+      <c r="A10" s="27"/>
+      <c r="B10" s="22"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="34"/>
-      <c r="B11" s="29"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="18" t="str">
+      <c r="A11" s="27"/>
+      <c r="B11" s="22"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="29"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="18" t="str">
+      <c r="A12" s="27"/>
+      <c r="B12" s="22"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="29"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="18" t="str">
+      <c r="A13" s="27"/>
+      <c r="B13" s="22"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="18" t="str">
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F15" s="18" t="str">
+      <c r="F15" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F16" s="18" t="str">
+      <c r="F16" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17" s="18" t="str">
+      <c r="F17" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F18" s="18" t="str">
+      <c r="F18" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" s="18" t="str">
+      <c r="F19" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" s="18" t="str">
+      <c r="F20" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F21" s="18" t="str">
+      <c r="F21" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F22" s="18" t="str">
+      <c r="F22" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F23" s="18" t="str">
+      <c r="F23" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24" s="18" t="str">
+      <c r="F24" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>

--- a/apps/home/homepage/fixtures/roinsight.xlsx
+++ b/apps/home/homepage/fixtures/roinsight.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammad.hamoud\Desktop\ng\backend\project\apps\home\homepage\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121F2AB0-4DBE-4C6C-B3ED-9DC719BB3FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D861D04A-94FA-4254-8338-AEEEBF4E94B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="660" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="660" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="528">
   <si>
     <t>name</t>
   </si>
@@ -911,12 +911,6 @@
     <t>قم بتحقيق أقصى قدر من إيرادات فندقك مع خدماتنا المستنيرة. نحن نحسن التسعير وقنوات التوزيع، مما يزيد من معدلات الإشغال والربحية. استراتيجياتنا المخصصة تضمن نمواً قابلاً للقياس في الإيرادات، مما يساعدك على البقاء في المقدمة.</t>
   </si>
   <si>
-    <t>We provide a comprehensive overview of popular data science and business intelligence tools. From data visualization to advanced analytics and machine learning, it covers everything needed to make informed decisions about tool selection. Python is a high-level interpreted language, while R is used for statistical computing and graphics. Tableau offers data visualization and analytics, PowerBI is a business analytics service by Microsoft, and Excel is a widely-used spreadsheet software.</t>
-  </si>
-  <si>
-    <t>نحن نقدم نظرة شاملة على الأدوات الشهيرة في علم البيانات والذكاء التجاري. من تصور البيانات إلى التحليلات المتقدمة وتعلم الآلة، يغطي كل ما يلزم لاتخاذ قرارات مستنيرة حول اختيار الأدوات. بايثون هي لغة مترجمة مستوى عالٍ، بينما يستخدم R في الحوسبة الإحصائية والرسومات. تقدم Tableau تصور البيانات والتحليلات، بينما يعد PowerBI خدمة تحليلات الأعمال التي تقدمها مايكروسوفت، ويُعتبر Excel برنامج جداول بيانات معروف عالميًا.</t>
-  </si>
-  <si>
     <t>Pricing Plans</t>
   </si>
   <si>
@@ -1455,6 +1449,192 @@
   </si>
   <si>
     <t>enterprise_reports</t>
+  </si>
+  <si>
+    <t>slogan</t>
+  </si>
+  <si>
+    <t>Refined Intelligence</t>
+  </si>
+  <si>
+    <t>Discover leading data science and business intelligence tools for analytics, visualization, and informed decision-making</t>
+  </si>
+  <si>
+    <t>اكتشف أبرز أدوات علم البيانات وذكاء الأعمال للتحليلات والتصور البياني واتخاذ القرارات المستنيرة.</t>
+  </si>
+  <si>
+    <t>Mahmoud Alhamoud</t>
+  </si>
+  <si>
+    <t>Director Sales and Marketing</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>محمود الحمود</t>
+  </si>
+  <si>
+    <t>مدير المبيعات والتسويق</t>
+  </si>
+  <si>
+    <t>mahmoud@hamouds.com</t>
+  </si>
+  <si>
+    <t>962790447208</t>
+  </si>
+  <si>
+    <t>Jordan, Amman</t>
+  </si>
+  <si>
+    <t>https://linkedin.com</t>
+  </si>
+  <si>
+    <t>https://github.com/roinsight</t>
+  </si>
+  <si>
+    <t>mahmoud</t>
+  </si>
+  <si>
+    <t>Amjad Muhammad Ali</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>أمجد محمد علي</t>
+  </si>
+  <si>
+    <t>مدير إداري</t>
+  </si>
+  <si>
+    <t>amjad@hamouds.com</t>
+  </si>
+  <si>
+    <t>United Arab Emirates, Dubai</t>
+  </si>
+  <si>
+    <t>amjad</t>
+  </si>
+  <si>
+    <t>Ashraf Salama</t>
+  </si>
+  <si>
+    <t>Regional Director</t>
+  </si>
+  <si>
+    <t>أشرف سلامة</t>
+  </si>
+  <si>
+    <t>مدير إقليمي</t>
+  </si>
+  <si>
+    <t>ashraf@hamouds.com</t>
+  </si>
+  <si>
+    <t>Lebanon, Beirut</t>
+  </si>
+  <si>
+    <t>ashraf</t>
+  </si>
+  <si>
+    <t>Sindbad stores</t>
+  </si>
+  <si>
+    <t>Your one-stop destination for all things exclusive in Jordan! Explore our wide range of products designed to make your life easier and more efficient. From cutting-edge gadgets to essential appliances, we've got you covered. Shop with confidence and convenience, knowing that quality and reliability are our top priorities.</t>
+  </si>
+  <si>
+    <t>https://sindbadstores.com/</t>
+  </si>
+  <si>
+    <t>سندباد ستورز</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> وجهة واحدة لجميع المنتجات الحصرية في الأردن! استكشف مجموعتنا الواسعة من المنتجات المصممة لتسهيل حياتك وجعلها أكثر كفاءة. من الأجهزة المبتكرة إلى الأجهزة الأساسية، نحن هنا لنلبي احتياجاتك. تسوق بثقة وراحة بال، على علم بأن الجودة والموثوقية هما أولويتنا الأساسية.</t>
+  </si>
+  <si>
+    <t>sindbadstores</t>
+  </si>
+  <si>
+    <t>Darwash Co</t>
+  </si>
+  <si>
+    <t>DarwashCo offers top-quality prefab solutions in the Gulf region. Our expert team specializes in efficient Pre-Fabricated Houses. Choose DarwashCo for simplicity, precision manufacturing, and innovative prefab construction, making your project cost-effective and hassle-free.</t>
+  </si>
+  <si>
+    <t>https://darwashco.com/</t>
+  </si>
+  <si>
+    <t>دروش كو</t>
+  </si>
+  <si>
+    <t>دارواشكو تقدم حلول مسبقة الصنع عالية الجودة في منطقة الخليج. يتخصص فريقنا المتخصص في بيوت مسبقة الصنع فعالة. اختر دارواشكو للبساطة والتصنيع الدقيق والبناء المسبق المبتكر، مما يجعل مشروعك فعالًا من حيث التكلفة وخاليًا من المتاعب.</t>
+  </si>
+  <si>
+    <t>darwashco</t>
+  </si>
+  <si>
+    <t>Sarah Johnson</t>
+  </si>
+  <si>
+    <t>Head of Digital Strategy with 10+ years experience.</t>
+  </si>
+  <si>
+    <t>Head of Digital Strategy</t>
+  </si>
+  <si>
+    <t>NovaTech Solutions</t>
+  </si>
+  <si>
+    <t>Working with this team transformed our online presence.</t>
+  </si>
+  <si>
+    <t>fa-quote-right</t>
+  </si>
+  <si>
+    <t>سارة جونسون</t>
+  </si>
+  <si>
+    <t>رئيسة الاستراتيجية الرقمية بخبرة تزيد عن 10 سنوات.</t>
+  </si>
+  <si>
+    <t>رئيسة الاستراتيجية الرقمية</t>
+  </si>
+  <si>
+    <t>نوفاتك سوليوشنز</t>
+  </si>
+  <si>
+    <t>العمل مع هذا الفريق غيّر حضورنا الرقمي بالكامل.</t>
+  </si>
+  <si>
+    <t>Ahmed Khaled</t>
+  </si>
+  <si>
+    <t>Marketing Director focused on growth and ROI.</t>
+  </si>
+  <si>
+    <t>Marketing Director</t>
+  </si>
+  <si>
+    <t>GrowthHub</t>
+  </si>
+  <si>
+    <t>Professional, efficient, and results-driven team.</t>
+  </si>
+  <si>
+    <t>أحمد خالد</t>
+  </si>
+  <si>
+    <t>مدير التسويق يركز على النمو والعائد على الاستثمار.</t>
+  </si>
+  <si>
+    <t>مدير التسويق</t>
+  </si>
+  <si>
+    <t>جروث هب</t>
+  </si>
+  <si>
+    <t>فريق احترافي وفعال يحقق نتائج ملموسة.</t>
   </si>
 </sst>
 </file>
@@ -1598,7 +1778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1669,6 +1849,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2092,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2103,7 +2286,7 @@
     <col min="6" max="6" width="71.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2134,13 +2317,16 @@
       <c r="J1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" ht="300" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>286</v>
+      <c r="B2" s="29" t="s">
+        <v>468</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>4</v>
@@ -2148,14 +2334,17 @@
       <c r="E2" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>287</v>
+      <c r="F2" t="s">
+        <v>469</v>
       </c>
       <c r="G2" s="8">
         <v>1208878</v>
       </c>
       <c r="I2" s="8">
         <v>994842</v>
+      </c>
+      <c r="K2" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -2399,20 +2588,21 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED841FD-3F18-44C9-A919-AF4192647E2D}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2451,6 +2641,76 @@
       </c>
       <c r="L1" s="7" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" t="s">
+        <v>512</v>
+      </c>
+      <c r="G2" t="s">
+        <v>513</v>
+      </c>
+      <c r="H2" t="s">
+        <v>514</v>
+      </c>
+      <c r="I2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J2" t="s">
+        <v>516</v>
+      </c>
+      <c r="K2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3" t="s">
+        <v>522</v>
+      </c>
+      <c r="F3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G3" t="s">
+        <v>523</v>
+      </c>
+      <c r="H3" t="s">
+        <v>524</v>
+      </c>
+      <c r="I3" t="s">
+        <v>525</v>
+      </c>
+      <c r="J3" t="s">
+        <v>526</v>
+      </c>
+      <c r="K3" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -2580,19 +2840,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" t="s">
         <v>288</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>289</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>290</v>
-      </c>
-      <c r="E2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F2" t="s">
-        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -2636,7 +2896,7 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2645,52 +2905,52 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F1" t="s">
         <v>294</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>295</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>296</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>297</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>298</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>299</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>300</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>301</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>302</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>303</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>304</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>305</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>306</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>307</v>
-      </c>
-      <c r="R1" t="s">
-        <v>308</v>
-      </c>
-      <c r="S1" t="s">
-        <v>309</v>
       </c>
       <c r="T1" t="s">
         <v>17</v>
@@ -2702,19 +2962,19 @@
         <v>6</v>
       </c>
       <c r="W1" t="s">
+        <v>308</v>
+      </c>
+      <c r="X1" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y1" t="s">
         <v>310</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>311</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>312</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>314</v>
       </c>
       <c r="AB1" t="s">
         <v>41</v>
@@ -2722,31 +2982,31 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D2" t="s">
         <v>315</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>316</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>317</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>318</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>319</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>320</v>
-      </c>
-      <c r="I2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J2" t="s">
-        <v>322</v>
       </c>
       <c r="K2">
         <v>49</v>
@@ -2776,57 +3036,57 @@
         <v>1</v>
       </c>
       <c r="U2" t="s">
+        <v>321</v>
+      </c>
+      <c r="V2" t="s">
+        <v>322</v>
+      </c>
+      <c r="W2" t="s">
         <v>323</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>324</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Z2" t="s">
         <v>325</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB2" t="s">
         <v>326</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>327</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D3" t="s">
         <v>329</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>330</v>
       </c>
-      <c r="D3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E3" t="s">
-        <v>332</v>
-      </c>
       <c r="F3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H3" t="s">
         <v>318</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>319</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>320</v>
-      </c>
-      <c r="I3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J3" t="s">
-        <v>322</v>
       </c>
       <c r="K3">
         <v>149</v>
@@ -2856,60 +3116,60 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
+        <v>331</v>
+      </c>
+      <c r="V3" t="s">
+        <v>332</v>
+      </c>
+      <c r="W3" t="s">
         <v>333</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X3" t="s">
         <v>334</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB3" t="s">
         <v>335</v>
-      </c>
-      <c r="X3" t="s">
-        <v>336</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>326</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>327</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" t="s">
         <v>338</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>339</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4" t="s">
         <v>340</v>
       </c>
-      <c r="E4" t="s">
-        <v>341</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>318</v>
       </c>
-      <c r="G4" t="s">
-        <v>342</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>319</v>
+      </c>
+      <c r="J4" t="s">
         <v>320</v>
-      </c>
-      <c r="I4" t="s">
-        <v>321</v>
-      </c>
-      <c r="J4" t="s">
-        <v>322</v>
       </c>
       <c r="K4">
         <v>299</v>
@@ -2939,60 +3199,60 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
+        <v>341</v>
+      </c>
+      <c r="V4" t="s">
+        <v>342</v>
+      </c>
+      <c r="W4" t="s">
         <v>343</v>
       </c>
-      <c r="V4" t="s">
+      <c r="X4" t="s">
         <v>344</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Y4" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z4" t="s">
         <v>345</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AA4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB4" t="s">
         <v>346</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>326</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D5" t="s">
         <v>349</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>350</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>351</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>352</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I5" t="s">
         <v>353</v>
       </c>
-      <c r="G5" t="s">
-        <v>354</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>320</v>
-      </c>
-      <c r="I5" t="s">
-        <v>355</v>
-      </c>
-      <c r="J5" t="s">
-        <v>322</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3010,28 +3270,28 @@
         <v>4</v>
       </c>
       <c r="T5" t="s">
+        <v>354</v>
+      </c>
+      <c r="U5" t="s">
+        <v>355</v>
+      </c>
+      <c r="V5" t="s">
         <v>356</v>
       </c>
-      <c r="U5" t="s">
+      <c r="W5" t="s">
         <v>357</v>
       </c>
-      <c r="V5" t="s">
+      <c r="X5" t="s">
         <v>358</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>359</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Z5" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA5" t="s">
         <v>360</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>361</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>320</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3060,7 +3320,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -3069,16 +3329,16 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F1" t="s">
         <v>364</v>
       </c>
-      <c r="E1" t="s">
-        <v>365</v>
-      </c>
-      <c r="F1" t="s">
-        <v>366</v>
-      </c>
       <c r="G1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
@@ -3090,7 +3350,7 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L1" t="s">
         <v>41</v>
@@ -3098,16 +3358,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" t="s">
         <v>368</v>
-      </c>
-      <c r="C2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D2" t="s">
-        <v>370</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3116,27 +3376,27 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J2" t="s">
+        <v>370</v>
+      </c>
+      <c r="L2" t="s">
         <v>371</v>
-      </c>
-      <c r="J2" t="s">
-        <v>372</v>
-      </c>
-      <c r="L2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3145,27 +3405,27 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L3" t="s">
         <v>376</v>
-      </c>
-      <c r="J3" t="s">
-        <v>377</v>
-      </c>
-      <c r="L3" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3174,27 +3434,27 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
+        <v>379</v>
+      </c>
+      <c r="J4" t="s">
+        <v>380</v>
+      </c>
+      <c r="L4" t="s">
         <v>381</v>
-      </c>
-      <c r="J4" t="s">
-        <v>382</v>
-      </c>
-      <c r="L4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3203,27 +3463,27 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
+        <v>384</v>
+      </c>
+      <c r="J5" t="s">
+        <v>385</v>
+      </c>
+      <c r="L5" t="s">
         <v>386</v>
-      </c>
-      <c r="J5" t="s">
-        <v>387</v>
-      </c>
-      <c r="L5" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3232,27 +3492,27 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J6" t="s">
+        <v>390</v>
+      </c>
+      <c r="L6" t="s">
         <v>391</v>
-      </c>
-      <c r="J6" t="s">
-        <v>392</v>
-      </c>
-      <c r="L6" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3261,27 +3521,27 @@
         <v>3</v>
       </c>
       <c r="I7" t="s">
+        <v>394</v>
+      </c>
+      <c r="J7" t="s">
+        <v>395</v>
+      </c>
+      <c r="L7" t="s">
         <v>396</v>
-      </c>
-      <c r="J7" t="s">
-        <v>397</v>
-      </c>
-      <c r="L7" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -3290,27 +3550,27 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
+        <v>399</v>
+      </c>
+      <c r="J8" t="s">
+        <v>400</v>
+      </c>
+      <c r="L8" t="s">
         <v>401</v>
-      </c>
-      <c r="J8" t="s">
-        <v>402</v>
-      </c>
-      <c r="L8" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3319,27 +3579,27 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
+        <v>404</v>
+      </c>
+      <c r="J9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L9" t="s">
         <v>406</v>
-      </c>
-      <c r="J9" t="s">
-        <v>407</v>
-      </c>
-      <c r="L9" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3348,27 +3608,27 @@
         <v>3</v>
       </c>
       <c r="I10" t="s">
+        <v>409</v>
+      </c>
+      <c r="J10" t="s">
+        <v>410</v>
+      </c>
+      <c r="L10" t="s">
         <v>411</v>
-      </c>
-      <c r="J10" t="s">
-        <v>412</v>
-      </c>
-      <c r="L10" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D11" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3377,27 +3637,27 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
+        <v>414</v>
+      </c>
+      <c r="J11" t="s">
+        <v>415</v>
+      </c>
+      <c r="L11" t="s">
         <v>416</v>
-      </c>
-      <c r="J11" t="s">
-        <v>417</v>
-      </c>
-      <c r="L11" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3406,27 +3666,27 @@
         <v>2</v>
       </c>
       <c r="I12" t="s">
+        <v>419</v>
+      </c>
+      <c r="J12" t="s">
+        <v>420</v>
+      </c>
+      <c r="L12" t="s">
         <v>421</v>
-      </c>
-      <c r="J12" t="s">
-        <v>422</v>
-      </c>
-      <c r="L12" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -3435,13 +3695,13 @@
         <v>3</v>
       </c>
       <c r="I13" t="s">
+        <v>424</v>
+      </c>
+      <c r="J13" t="s">
+        <v>425</v>
+      </c>
+      <c r="L13" t="s">
         <v>426</v>
-      </c>
-      <c r="J13" t="s">
-        <v>427</v>
-      </c>
-      <c r="L13" t="s">
-        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -3468,25 +3728,25 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" t="s">
         <v>429</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>430</v>
       </c>
-      <c r="E1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F1" t="s">
-        <v>432</v>
-      </c>
       <c r="G1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
@@ -3495,10 +3755,10 @@
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L1" t="s">
         <v>41</v>
@@ -3506,16 +3766,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D2" t="s">
         <v>435</v>
-      </c>
-      <c r="C2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D2" t="s">
-        <v>437</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3524,27 +3784,27 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J2" t="s">
+        <v>437</v>
+      </c>
+      <c r="L2" t="s">
         <v>438</v>
-      </c>
-      <c r="J2" t="s">
-        <v>439</v>
-      </c>
-      <c r="L2" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3553,27 +3813,27 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" t="s">
+        <v>442</v>
+      </c>
+      <c r="L3" t="s">
         <v>443</v>
-      </c>
-      <c r="J3" t="s">
-        <v>444</v>
-      </c>
-      <c r="L3" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E4">
         <v>20</v>
@@ -3582,27 +3842,27 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" t="s">
         <v>435</v>
-      </c>
-      <c r="C5" t="s">
-        <v>450</v>
-      </c>
-      <c r="D5" t="s">
-        <v>437</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -3611,27 +3871,27 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -3640,27 +3900,27 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3669,27 +3929,27 @@
         <v>3</v>
       </c>
       <c r="I7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D8" t="s">
         <v>435</v>
-      </c>
-      <c r="C8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D8" t="s">
-        <v>437</v>
       </c>
       <c r="E8">
         <v>20</v>
@@ -3698,27 +3958,27 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E9">
         <v>25</v>
@@ -3727,123 +3987,123 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="I10" t="s">
+        <v>458</v>
+      </c>
+      <c r="K10" t="s">
+        <v>459</v>
+      </c>
+      <c r="L10" t="s">
         <v>460</v>
-      </c>
-      <c r="K10" t="s">
-        <v>461</v>
-      </c>
-      <c r="L10" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="I12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K12" t="s">
+        <v>462</v>
+      </c>
+      <c r="L12" t="s">
         <v>464</v>
-      </c>
-      <c r="L12" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -4010,22 +4270,51 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="15"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="8"/>
+    <row r="2" spans="1:7" ht="199.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="171" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
@@ -4098,8 +4387,11 @@
   <conditionalFormatting sqref="E1:G1">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{7823058C-3890-4396-B507-3DCF2AA31BC1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4355,38 +4647,135 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="J2" s="6"/>
-      <c r="K2" s="9"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
+      <c r="A2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H2" t="s">
+        <v>474</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="L2" t="s">
+        <v>477</v>
+      </c>
+      <c r="M2" t="str">
+        <f>"https://wa.me/"&amp;K2&amp;"?text=I'm%20interested%20in%20hamouds.com"</f>
+        <v>https://wa.me/962790447208?text=I'm%20interested%20in%20hamouds.com</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>478</v>
+      </c>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="R2" s="6" t="s">
+        <v>479</v>
+      </c>
       <c r="S2" s="6"/>
+      <c r="T2" t="s">
+        <v>480</v>
+      </c>
       <c r="V2" s="26" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="J3" s="6"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="N3" s="6"/>
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H3" t="s">
+        <v>484</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M4" si="0">"https://wa.me/"&amp;K3&amp;"?text=I'm%20interested%20in%20hamouds.com"</f>
+        <v>https://wa.me/971503250175?text=I'm%20interested%20in%20hamouds.com</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>478</v>
+      </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="R3" s="6" t="s">
+        <v>479</v>
+      </c>
       <c r="S3" s="6"/>
+      <c r="T3" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="J4" s="6"/>
-      <c r="K4" s="9"/>
-      <c r="N4" s="6"/>
+      <c r="A4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" t="s">
+        <v>489</v>
+      </c>
+      <c r="E4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H4" t="s">
+        <v>491</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="K4" s="9">
+        <v>96181525921</v>
+      </c>
+      <c r="L4" t="s">
+        <v>493</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="0"/>
+        <v>https://wa.me/96181525921?text=I'm%20interested%20in%20hamouds.com</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>478</v>
+      </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="R4" s="6" t="s">
+        <v>479</v>
+      </c>
       <c r="S4" s="6"/>
+      <c r="T4" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J5" s="6"/>
@@ -4456,8 +4845,15 @@
   <conditionalFormatting sqref="T1">
     <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{5556BFE9-283E-4337-9312-91FD8ABEC071}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{A14F185F-B479-4203-9F7F-83A4556D1C4D}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{BAB2530A-B075-4655-8E02-A64649274A31}"/>
+    <hyperlink ref="N2" r:id="rId4" xr:uid="{3C9409AD-F59B-4DBE-BB52-8CC6758D7819}"/>
+    <hyperlink ref="N3:N4" r:id="rId5" display="https://linkedin.com" xr:uid="{299B2202-42B7-4EBD-A154-E7310BE0650E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
